--- a/PSNR_Table.xlsx
+++ b/PSNR_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91F1384D-E72F-43A9-80A2-61B15504E8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{304A856B-63E1-47BF-AD30-4801F319EB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BC4F2C0C-3ED4-41BD-AD4F-2EA902663761}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C42C7673-F975-4D29-8E2D-17A5CCC3BEEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -445,7 +448,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A4BBBB-55B7-40EA-8F9C-449EBFF8C774}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71012450-2D3A-43F2-A256-92D44450F4A3}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -599,7 +602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D64C416-842B-42BD-BB4F-D4DE75F9262A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC352CA-4AFE-4255-A705-0BE28F22FF56}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -608,7 +611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CF2026C-D8B1-4881-9DF1-97E00495DF52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27453D16-1605-4A3C-BCCE-27E4501D5F68}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
